--- a/data/chapter35_Quarto.xlsx
+++ b/data/chapter35_Quarto.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R入門\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AAD84B7-4D24-4E0B-833A-076A8C677255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5EA8205-8BEF-4CC8-9446-752FBF4314EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{45AADD67-DB4F-41EA-A38B-1FE6C1AF3A60}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="16440" xr2:uid="{45AADD67-DB4F-41EA-A38B-1FE6C1AF3A60}"/>
   </bookViews>
   <sheets>
     <sheet name="markdown" sheetId="1" r:id="rId1"/>
@@ -1660,6 +1655,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1670,6 +1666,7 @@
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1873,6 +1870,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1991,5 +1989,6 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>